--- a/SGC-CKN/Excel/730ecf38-d9bf-4842-89af-62ea53583c13_Cọc_khoan_nhồi_đại_trà_P7-82_D800_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/730ecf38-d9bf-4842-89af-62ea53583c13_Cọc_khoan_nhồi_đại_trà_P7-82_D800_21-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
   <si>
     <t>Dự án</t>
   </si>
@@ -176,7 +176,7 @@
   </si>
   <si>
     <t xml:space="preserve">21:17
-21/03/2026</t>
+20/03/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -185,22 +185,24 @@
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">23:60
-21/03/2026</t>
+    <t xml:space="preserve">23:00
+20/03/2026</t>
+  </si>
+  <si>
+    <t>Chạm sỏi</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
     <t>Cuội đa màu sắc TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:00
-21/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:46
 21/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kết thúc </t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1221,10 +1223,10 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-7.21</v>
+        <v>-6.5</v>
       </c>
       <c r="H11" s="5">
         <v>0.5</v>
@@ -1256,10 +1258,10 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-7.21</v>
+        <v>-6.5</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.21</v>
+        <v>-8.5</v>
       </c>
       <c r="H12" s="9">
         <v>0.25</v>
@@ -1291,10 +1293,10 @@
         <v>36</v>
       </c>
       <c r="F13" s="12">
-        <v>-9.21</v>
+        <v>-8.5</v>
       </c>
       <c r="G13" s="12">
-        <v>-17.51</v>
+        <v>-16.8</v>
       </c>
       <c r="H13" s="12">
         <v>0.67</v>
@@ -1326,10 +1328,10 @@
         <v>39</v>
       </c>
       <c r="F14" s="15">
-        <v>-17.51</v>
+        <v>-16.8</v>
       </c>
       <c r="G14" s="15">
-        <v>-22.71</v>
+        <v>-22.002</v>
       </c>
       <c r="H14" s="15">
         <v>0.58</v>
@@ -1338,7 +1340,7 @@
         <v>5.2</v>
       </c>
       <c r="J14" s="8">
-        <v>8.91</v>
+        <v>8.92</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
@@ -1361,10 +1363,10 @@
         <v>42</v>
       </c>
       <c r="F15" s="18">
-        <v>-22.71</v>
+        <v>-22.002</v>
       </c>
       <c r="G15" s="18">
-        <v>-26.81</v>
+        <v>-26.1</v>
       </c>
       <c r="H15" s="18">
         <v>0.5</v>
@@ -1396,10 +1398,10 @@
         <v>45</v>
       </c>
       <c r="F16" s="21">
-        <v>-26.81</v>
+        <v>-26.1</v>
       </c>
       <c r="G16" s="21">
-        <v>-34.81</v>
+        <v>-34.1</v>
       </c>
       <c r="H16" s="21">
         <v>0.83</v>
@@ -1431,10 +1433,10 @@
         <v>48</v>
       </c>
       <c r="F17" s="24">
-        <v>-34.81</v>
+        <v>-34.1</v>
       </c>
       <c r="G17" s="24">
-        <v>-37.81</v>
+        <v>-37.1</v>
       </c>
       <c r="H17" s="24">
         <v>0.92</v>
@@ -1466,10 +1468,10 @@
         <v>51</v>
       </c>
       <c r="F18" s="28">
-        <v>-37.81</v>
+        <v>-37.1</v>
       </c>
       <c r="G18" s="28">
-        <v>-39.91</v>
+        <v>-39.2</v>
       </c>
       <c r="H18" s="28">
         <v>3.2</v>
@@ -1501,62 +1503,62 @@
         <v>54</v>
       </c>
       <c r="F19" s="32">
-        <v>-39.91</v>
+        <v>-39.2</v>
       </c>
       <c r="G19" s="32">
-        <v>-44.21</v>
+        <v>-43.5</v>
       </c>
       <c r="H19" s="32">
-        <v>2.72</v>
+        <v>1.72</v>
       </c>
       <c r="I19" s="32">
         <v>4.3</v>
       </c>
       <c r="J19" s="27">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="35" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>58</v>
       </c>
       <c r="F20" s="35">
-        <v>-44.21</v>
+        <v>-43.5</v>
       </c>
       <c r="G20" s="35">
-        <v>-45.56</v>
+        <v>-44.86</v>
       </c>
       <c r="H20" s="35">
         <v>2.77</v>
       </c>
       <c r="I20" s="35">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="J20" s="31">
         <v>0.49</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1662,31 +1664,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1703,10 +1705,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-7.21</v>
+        <v>-6.5</v>
       </c>
       <c r="G2" s="5">
         <v>0.5</v>
@@ -1732,10 +1734,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-7.21</v>
+        <v>-6.5</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.21</v>
+        <v>-8.5</v>
       </c>
       <c r="G3" s="9">
         <v>0.25</v>
@@ -1761,10 +1763,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-9.21</v>
+        <v>-8.5</v>
       </c>
       <c r="F4" s="12">
-        <v>-17.51</v>
+        <v>-16.8</v>
       </c>
       <c r="G4" s="12">
         <v>0.67</v>
@@ -1790,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>-17.51</v>
+        <v>-16.8</v>
       </c>
       <c r="F5" s="15">
-        <v>-22.71</v>
+        <v>-22</v>
       </c>
       <c r="G5" s="15">
         <v>0.58</v>
@@ -1802,7 +1804,7 @@
         <v>5.2</v>
       </c>
       <c r="I5" s="8">
-        <v>8.91</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1819,10 +1821,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>-22.71</v>
+        <v>-22</v>
       </c>
       <c r="F6" s="18">
-        <v>-26.81</v>
+        <v>-26.1</v>
       </c>
       <c r="G6" s="18">
         <v>0.5</v>
@@ -1848,10 +1850,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-26.81</v>
+        <v>-26.1</v>
       </c>
       <c r="F7" s="21">
-        <v>-34.81</v>
+        <v>-34.1</v>
       </c>
       <c r="G7" s="21">
         <v>0.83</v>
@@ -1877,10 +1879,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="24">
-        <v>-34.81</v>
+        <v>-34.1</v>
       </c>
       <c r="F8" s="24">
-        <v>-37.81</v>
+        <v>-37.1</v>
       </c>
       <c r="G8" s="24">
         <v>0.92</v>
@@ -1906,10 +1908,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-37.81</v>
+        <v>-37.1</v>
       </c>
       <c r="F9" s="28">
-        <v>-39.91</v>
+        <v>-39.2</v>
       </c>
       <c r="G9" s="28">
         <v>3.2</v>
@@ -1935,19 +1937,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="32">
-        <v>-39.91</v>
+        <v>-39.2</v>
       </c>
       <c r="F10" s="32">
-        <v>-44.21</v>
+        <v>-43.5</v>
       </c>
       <c r="G10" s="32">
-        <v>2.72</v>
+        <v>1.72</v>
       </c>
       <c r="H10" s="32">
         <v>4.3</v>
       </c>
       <c r="I10" s="27">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1958,22 +1960,22 @@
         <v>11</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" s="35">
         <v>1</v>
       </c>
       <c r="E11" s="35">
-        <v>-44.21</v>
+        <v>-43.5</v>
       </c>
       <c r="F11" s="35">
-        <v>-45.56</v>
+        <v>-44.86</v>
       </c>
       <c r="G11" s="35">
         <v>2.77</v>
       </c>
       <c r="H11" s="35">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="I11" s="31">
         <v>0.49</v>
@@ -1981,7 +1983,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>30</v>
@@ -1993,19 +1995,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
-        <v>-45.56</v>
+        <v>-44.86</v>
       </c>
       <c r="G12" s="40">
-        <v>12.93</v>
+        <v>11.93</v>
       </c>
       <c r="H12" s="40">
-        <v>44.85</v>
+        <v>44.86</v>
       </c>
       <c r="I12" s="40">
-        <v>3.47</v>
+        <v>3.76</v>
       </c>
     </row>
   </sheetData>
